--- a/output/pdf_financials_xlsx/MAU.xlsx
+++ b/output/pdf_financials_xlsx/MAU.xlsx
@@ -769,16 +769,16 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>23.489736</v>
+        <v>-23.489736</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>9783.215</v>
+        <v>-9783.215</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>24.42</v>
+        <v>-24.42</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>67.771</v>
+        <v>-67.771</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>49.05</v>
@@ -803,7 +803,7 @@
         <v>-0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-98.09999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -877,19 +877,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>23.489736</v>
+        <v>-23.489736</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>9783.215</v>
+        <v>-9783.215</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>24.42</v>
+        <v>-24.42</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>67.771</v>
+        <v>-67.771</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>49.05</v>
+        <v>-49.05</v>
       </c>
     </row>
     <row r="21">
@@ -943,19 +943,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>23.489736</v>
+        <v>-23.489736</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>9783.215</v>
+        <v>-9783.215</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>24.42</v>
+        <v>-24.42</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>67.771</v>
+        <v>-67.771</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>49.05</v>
+        <v>-49.05</v>
       </c>
     </row>
     <row r="24">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>106.771527</v>
+        <v>-106.771527</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>108702.388889</v>
+        <v>-108702.388889</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>174.428571</v>
+        <v>-174.428571</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -1043,16 +1043,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>23.489736</v>
+        <v>-23.489736</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>9783.215</v>
+        <v>-9783.215</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>24.946</v>
+        <v>-23.894</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>71.13200000000001</v>
+        <v>-64.41</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>49.05</v>
@@ -1087,16 +1087,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>23.670743</v>
+        <v>-23.308729</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>9974.191999999999</v>
+        <v>-9592.237999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>25.177</v>
+        <v>-23.663</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>71.42700000000001</v>
+        <v>-64.11499999999999</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>49.265</v>
@@ -1141,19 +1141,19 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32">
@@ -2781,7 +2781,7 @@
         <v>-67.771</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>49.05</v>
+        <v>-49.05</v>
       </c>
     </row>
     <row r="100">
@@ -11345,7 +11345,7 @@
         </is>
       </c>
       <c r="I186" s="5" t="n">
-        <v>49.05</v>
+        <v>-49.05</v>
       </c>
     </row>
     <row r="187">
@@ -11476,7 +11476,7 @@
         </is>
       </c>
       <c r="I189" s="5" t="n">
-        <v>49.05</v>
+        <v>-49.05</v>
       </c>
     </row>
     <row r="190">
@@ -12125,16 +12125,16 @@
         </is>
       </c>
       <c r="E206" s="5" t="n">
-        <v>23.489736</v>
+        <v>-23.489736</v>
       </c>
       <c r="F206" s="5" t="n">
-        <v>9.783215</v>
+        <v>-9.783215</v>
       </c>
       <c r="G206" s="5" t="n">
-        <v>24.42</v>
+        <v>-24.42</v>
       </c>
       <c r="H206" s="5" t="n">
-        <v>67.771</v>
+        <v>-67.771</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
@@ -12258,10 +12258,10 @@
         </is>
       </c>
       <c r="G209" s="5" t="n">
-        <v>24.42</v>
+        <v>-24.42</v>
       </c>
       <c r="H209" s="5" t="n">
-        <v>67.771</v>
+        <v>-67.771</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
@@ -12381,10 +12381,10 @@
         </is>
       </c>
       <c r="G212" s="5" t="n">
-        <v>22.495</v>
+        <v>-22.495</v>
       </c>
       <c r="H212" s="5" t="n">
-        <v>67.54600000000001</v>
+        <v>-67.54600000000001</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
@@ -12508,10 +12508,10 @@
         </is>
       </c>
       <c r="G215" s="5" t="n">
-        <v>22.495</v>
+        <v>-22.495</v>
       </c>
       <c r="H215" s="5" t="n">
-        <v>67.54600000000001</v>
+        <v>-67.54600000000001</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -12955,10 +12955,10 @@
         </is>
       </c>
       <c r="F227" s="5" t="n">
-        <v>9783.215</v>
+        <v>-9783.215</v>
       </c>
       <c r="G227" s="5" t="n">
-        <v>24419.705</v>
+        <v>-24419.705</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -13098,13 +13098,13 @@
         </is>
       </c>
       <c r="E231" s="5" t="n">
-        <v>23.718619</v>
+        <v>-23.718619</v>
       </c>
       <c r="F231" s="5" t="n">
-        <v>9970.675999999999</v>
+        <v>-9970.675999999999</v>
       </c>
       <c r="G231" s="5" t="n">
-        <v>22494.797</v>
+        <v>-22494.797</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MAU.xlsx
+++ b/output/pdf_financials_xlsx/MAU.xlsx
@@ -681,10 +681,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0194</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-329.646</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>-0.526</v>
@@ -1017,23 +1017,21 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-106.771527</v>
+        <v>105.013162</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-108702.388889</v>
+        <v>112.000161</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-174.428571</v>
+        <v>178.187111</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F26" s="3" t="n">
+        <v>268.996635</v>
       </c>
     </row>
     <row r="27">
@@ -1043,10 +1041,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-23.489736</v>
+        <v>-23.470336</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-9783.215</v>
+        <v>-9453.569</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-23.894</v>
@@ -1087,10 +1085,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-23.308729</v>
+        <v>-23.289329</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-9592.237999999999</v>
+        <v>-9262.592000000001</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-23.663</v>
@@ -3329,10 +3327,10 @@
         <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.131</v>
       </c>
       <c r="F124" s="3" t="n">
         <v>0</v>
@@ -3351,10 +3349,10 @@
         <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.131</v>
       </c>
       <c r="F125" s="3" t="n">
         <v>0</v>
@@ -8468,7 +8466,11 @@
           <t>Lease payments (Note 11)</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -9475,7 +9477,11 @@
           <t>Lease payments (Note 9)</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -11747,7 +11753,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -12868,7 +12874,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E225" s="5" t="n">
@@ -12905,7 +12911,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -13172,7 +13178,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E233" s="5" t="n">

--- a/output/pdf_financials_xlsx/MAU.xlsx
+++ b/output/pdf_financials_xlsx/MAU.xlsx
@@ -2082,10 +2082,10 @@
         <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.187</v>
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
@@ -2106,10 +2106,10 @@
         <v>0</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>0.187</v>
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.041</v>
+        <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
         <v>0.031</v>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.002209944751381216</v>
+        <v>0.003134513473897847</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.01093320587883857</v>
+        <v>0.01651929740709762</v>
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
@@ -2946,16 +2946,16 @@
         <v>1.406447</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0.700359</v>
+        <v>700.359</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>1.177</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>9.609</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>6.996</v>
       </c>
     </row>
     <row r="108">
@@ -3031,13 +3031,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.169946</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-250.235</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-382.725</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>15.384</v>
@@ -3125,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>570.436</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -3555,13 +3555,13 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.169946</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-250.235</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-382.725</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>-15.384</v>
@@ -3577,13 +3577,13 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-22.851796</v>
+        <v>-23.021742</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-7929.489</v>
+        <v>-8179.724</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-17.411</v>
+        <v>-400.136</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-61.157</v>
@@ -5311,7 +5311,11 @@
           <t>Lease liabilities (Note 11)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -6107,7 +6111,11 @@
           <t>Lease liabilities (Note 9)</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -6859,7 +6867,11 @@
           <t>Share-based compensation expense (Note 16) 6,654</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -8027,7 +8039,11 @@
           <t>Share-based compensation expense (Note 14)</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -9280,7 +9296,11 @@
           <t>Share-based compensation expense (Note 12)</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -9397,7 +9417,11 @@
           <t>Purchase of equipment (Note 6)</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -9436,7 +9460,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -10200,7 +10228,11 @@
           <t>Purchase of equipment (Note 7)</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E159" s="5" t="n">
         <v>-0.169946</v>
       </c>
